--- a/results/components/gene_names/p2s12.xlsx
+++ b/results/components/gene_names/p2s12.xlsx
@@ -22,28 +22,28 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>Mitf</t>
-  </si>
-  <si>
-    <t>mask</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>lmd</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>bon</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
   </si>
 </sst>
 </file>

--- a/results/components/gene_names/p2s12.xlsx
+++ b/results/components/gene_names/p2s12.xlsx
@@ -22,28 +22,28 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>lmd</t>
-  </si>
-  <si>
-    <t>gl</t>
-  </si>
-  <si>
-    <t>bon</t>
-  </si>
-  <si>
-    <t>hpo</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>abd-A</t>
+    <t>Crk</t>
+  </si>
+  <si>
+    <t>RpL30</t>
+  </si>
+  <si>
+    <t>CG12301</t>
+  </si>
+  <si>
+    <t>dnc</t>
+  </si>
+  <si>
+    <t>brm</t>
+  </si>
+  <si>
+    <t>CG2681</t>
+  </si>
+  <si>
+    <t>Nrt</t>
+  </si>
+  <si>
+    <t>Akt1</t>
   </si>
 </sst>
 </file>
